--- a/Project_ETF/ETF_Investment_Portfolio/00981A/ETF_Investment_Portfolio_20260603.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00981A/ETF_Investment_Portfolio_20260603.xlsx
@@ -1261,17 +1261,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>高技</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>329,000</t>
+          <t>3,528,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1283,17 +1283,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>高技</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>3,528,000</t>
+          <t>1,642,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1305,17 +1305,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>1,642,000</t>
+          <t>329,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
